--- a/Zinc/6. Statistical data analysis/Toxicity plots/MLE_Cu_toxicity.xlsx
+++ b/Zinc/6. Statistical data analysis/Toxicity plots/MLE_Cu_toxicity.xlsx
@@ -33,19 +33,19 @@
     <t xml:space="preserve">mle_sd</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">Zn_chronic_tox_nM</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
